--- a/outputs/daily/hr_rankings_2026-10-17_full.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-17_full.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>51.5</v>
+        <v>53.3</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>32</v>
       </c>
       <c r="R2" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S2" t="n">
         <v>92.09999999999999</v>
@@ -996,8 +996,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -1036,7 +1044,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1060,7 +1068,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>50</v>
+        <v>51.8</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1084,7 +1092,7 @@
         <v>32</v>
       </c>
       <c r="R3" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S3" t="n">
         <v>95.5</v>
@@ -1272,8 +1280,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -1312,7 +1328,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1336,7 +1352,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>48.9</v>
+        <v>51.3</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1350,7 +1366,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -1360,10 +1376,10 @@
         <v>34.3</v>
       </c>
       <c r="R4" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S4" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T4" t="n">
         <v>50</v>
@@ -1373,39 +1389,35 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1548,8 +1560,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -1588,7 +1608,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1612,7 +1632,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>46.9</v>
+        <v>49.3</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1626,7 +1646,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1636,10 +1656,10 @@
         <v>34.3</v>
       </c>
       <c r="R5" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S5" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T5" t="n">
         <v>80</v>
@@ -1649,39 +1669,35 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -1824,8 +1840,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -1864,7 +1888,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1888,7 +1912,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>43.5</v>
+        <v>46</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1902,7 +1926,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -1912,10 +1936,10 @@
         <v>34.3</v>
       </c>
       <c r="R6" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S6" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
@@ -1925,39 +1949,35 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2100,8 +2120,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -2140,7 +2168,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2164,7 +2192,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>43.3</v>
+        <v>45.1</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2188,7 +2216,7 @@
         <v>32</v>
       </c>
       <c r="R7" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S7" t="n">
         <v>88.7</v>
@@ -2376,8 +2404,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -2416,7 +2452,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2440,7 +2476,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>43.3</v>
+        <v>45.1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2464,7 +2500,7 @@
         <v>32</v>
       </c>
       <c r="R8" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S8" t="n">
         <v>90.40000000000001</v>
@@ -2652,8 +2688,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -2672,7 +2716,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>José Ramírez</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2692,7 +2736,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -2716,7 +2760,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>41.7</v>
+        <v>44.2</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2730,7 +2774,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -2740,10 +2784,10 @@
         <v>32.5</v>
       </c>
       <c r="R9" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S9" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T9" t="n">
         <v>75</v>
@@ -2753,39 +2797,35 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2928,8 +2968,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -2968,7 +3016,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -2992,7 +3040,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>40.2</v>
+        <v>42.6</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3006,7 +3054,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -3016,10 +3064,10 @@
         <v>32.5</v>
       </c>
       <c r="R10" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S10" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T10" t="n">
         <v>75</v>
@@ -3029,39 +3077,35 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3204,8 +3248,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -3244,7 +3296,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3268,7 +3320,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>37.1</v>
+        <v>39.6</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3282,7 +3334,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -3292,10 +3344,10 @@
         <v>34.3</v>
       </c>
       <c r="R11" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S11" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T11" t="n">
         <v>80</v>
@@ -3305,39 +3357,35 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -3480,8 +3528,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -3520,7 +3576,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -3544,7 +3600,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>35.1</v>
+        <v>37.5</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3558,7 +3614,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -3568,10 +3624,10 @@
         <v>34.3</v>
       </c>
       <c r="R12" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S12" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T12" t="n">
         <v>80</v>
@@ -3581,39 +3637,35 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3756,8 +3808,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -3796,7 +3856,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -3820,7 +3880,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>34.8</v>
+        <v>36.6</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3844,7 +3904,7 @@
         <v>32</v>
       </c>
       <c r="R13" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S13" t="n">
         <v>81.90000000000001</v>
@@ -4032,8 +4092,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -4072,7 +4140,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4096,7 +4164,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>32.5</v>
+        <v>34.9</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4110,7 +4178,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -4120,10 +4188,10 @@
         <v>32.5</v>
       </c>
       <c r="R14" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S14" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T14" t="n">
         <v>75</v>
@@ -4133,39 +4201,35 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4308,8 +4372,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -4323,24 +4395,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>622761</t>
+          <t>690984</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jorge Mateo</t>
+          <t>Petey Halpin</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-10-18T00:08:00Z</t>
@@ -4348,7 +4420,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4358,12 +4430,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Shawn Armstrong</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>542888</t>
+          <t>607259</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -4372,7 +4444,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>30.7</v>
+        <v>33</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4386,62 +4458,58 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>23.3</v>
+        <v>7.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>32</v>
+        <v>34.3</v>
       </c>
       <c r="R15" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S15" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T15" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8</v>
+        <v>38.3</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4461,12 +4529,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -4476,12 +4544,12 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/16, 0 HR</t>
+          <t>Contact streak: 3/8 over last 7 games</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -4491,101 +4559,109 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>35.51</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>81.45</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>98.4476</t>
+          <t>93.4449</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3271</t>
+          <t>0.3143</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1223</t>
+          <t>0.0924</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.2522</t>
+          <t>0.2902</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>70.22</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>31.46</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>29.09</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1044</t>
+          <t>0.0707</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>33.38</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>0.3695</t>
+          <t>0.4114</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>0.1577</t>
+          <t>0.1502</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>29.92</t>
-        </is>
-      </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+          <t>28.96</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -4599,24 +4675,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>690984</t>
+          <t>622761</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Petey Halpin</t>
+          <t>Jorge Mateo</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-18T00:08:00Z</t>
@@ -4624,7 +4700,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -4634,12 +4710,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -4648,7 +4724,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>30.5</v>
+        <v>32.5</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4662,26 +4738,26 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>7.1</v>
+        <v>23.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>34.3</v>
+        <v>32</v>
       </c>
       <c r="R16" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S16" t="n">
         <v>47.9</v>
       </c>
       <c r="T16" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U16" t="n">
-        <v>38.3</v>
+        <v>0.8</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -4737,12 +4813,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -4752,12 +4828,12 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Contact streak: 3/8 over last 7 games</t>
+          <t>Last 7 games: 2/16, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -4767,101 +4843,109 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>6.76</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>35.51</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>81.45</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>93.4449</t>
+          <t>98.4476</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3143</t>
+          <t>0.3271</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.0924</t>
+          <t>0.1223</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.2902</t>
+          <t>0.2522</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>70.22</t>
+          <t>73.23</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>31.46</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>29.09</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.0707</t>
+          <t>0.1044</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>28.96</t>
-        </is>
-      </c>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+          <t>29.92</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -4900,7 +4984,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -4924,7 +5008,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>29.9</v>
+        <v>31.7</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -4948,7 +5032,7 @@
         <v>32</v>
       </c>
       <c r="R17" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S17" t="n">
         <v>71.7</v>
@@ -5136,8 +5220,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -5176,7 +5268,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -5200,7 +5292,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>29.8</v>
+        <v>31.6</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5224,7 +5316,7 @@
         <v>32</v>
       </c>
       <c r="R18" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S18" t="n">
         <v>59.8</v>
@@ -5412,8 +5504,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -5452,7 +5552,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -5476,7 +5576,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>27.3</v>
+        <v>29.1</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5500,7 +5600,7 @@
         <v>31.5</v>
       </c>
       <c r="R19" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S19" t="n">
         <v>40.2</v>
@@ -5688,8 +5788,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -6054,7 +6162,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -6078,7 +6186,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>51.5</v>
+        <v>53.3</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6102,7 +6210,7 @@
         <v>32</v>
       </c>
       <c r="R2" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S2" t="n">
         <v>92.09999999999999</v>
@@ -6290,8 +6398,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -6330,7 +6446,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -6354,7 +6470,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>50</v>
+        <v>51.8</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6378,7 +6494,7 @@
         <v>32</v>
       </c>
       <c r="R3" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S3" t="n">
         <v>95.5</v>
@@ -6566,8 +6682,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -6606,7 +6730,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -6630,7 +6754,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>48.9</v>
+        <v>51.3</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6644,7 +6768,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -6654,10 +6778,10 @@
         <v>34.3</v>
       </c>
       <c r="R4" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S4" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T4" t="n">
         <v>50</v>
@@ -6667,39 +6791,35 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6842,8 +6962,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -6882,7 +7010,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -6906,7 +7034,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>46.9</v>
+        <v>49.3</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -6920,7 +7048,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -6930,10 +7058,10 @@
         <v>34.3</v>
       </c>
       <c r="R5" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S5" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T5" t="n">
         <v>80</v>
@@ -6943,39 +7071,35 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -7118,8 +7242,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -7158,7 +7290,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -7182,7 +7314,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>43.5</v>
+        <v>46</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7196,7 +7328,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -7206,10 +7338,10 @@
         <v>34.3</v>
       </c>
       <c r="R6" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S6" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
@@ -7219,39 +7351,35 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7394,8 +7522,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -7434,7 +7570,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -7458,7 +7594,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>43.3</v>
+        <v>45.1</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7482,7 +7618,7 @@
         <v>32</v>
       </c>
       <c r="R7" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S7" t="n">
         <v>88.7</v>
@@ -7670,8 +7806,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -7710,7 +7854,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -7734,7 +7878,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>43.3</v>
+        <v>45.1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7758,7 +7902,7 @@
         <v>32</v>
       </c>
       <c r="R8" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S8" t="n">
         <v>90.40000000000001</v>
@@ -7946,8 +8090,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -7966,7 +8118,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>José Ramírez</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -7986,7 +8138,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -8010,7 +8162,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>41.7</v>
+        <v>44.2</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8024,7 +8176,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -8034,10 +8186,10 @@
         <v>32.5</v>
       </c>
       <c r="R9" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S9" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T9" t="n">
         <v>75</v>
@@ -8047,39 +8199,35 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8222,8 +8370,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -8262,7 +8418,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -8286,7 +8442,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>40.2</v>
+        <v>42.6</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8300,7 +8456,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -8310,10 +8466,10 @@
         <v>32.5</v>
       </c>
       <c r="R10" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S10" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T10" t="n">
         <v>75</v>
@@ -8323,39 +8479,35 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8498,8 +8650,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -8538,7 +8698,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -8562,7 +8722,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>37.1</v>
+        <v>39.6</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8576,7 +8736,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -8586,10 +8746,10 @@
         <v>34.3</v>
       </c>
       <c r="R11" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S11" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T11" t="n">
         <v>80</v>
@@ -8599,39 +8759,35 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -8774,8 +8930,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -8814,7 +8978,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -8838,7 +9002,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>35.1</v>
+        <v>37.5</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -8852,7 +9016,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -8862,10 +9026,10 @@
         <v>34.3</v>
       </c>
       <c r="R12" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S12" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T12" t="n">
         <v>80</v>
@@ -8875,39 +9039,35 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9050,8 +9210,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -9090,7 +9258,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -9114,7 +9282,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>34.8</v>
+        <v>36.6</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9138,7 +9306,7 @@
         <v>32</v>
       </c>
       <c r="R13" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S13" t="n">
         <v>81.90000000000001</v>
@@ -9326,8 +9494,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -9366,7 +9542,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -9390,7 +9566,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>32.5</v>
+        <v>34.9</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9404,7 +9580,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -9414,10 +9590,10 @@
         <v>32.5</v>
       </c>
       <c r="R14" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S14" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T14" t="n">
         <v>75</v>
@@ -9427,39 +9603,35 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9602,8 +9774,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -9617,24 +9797,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>622761</t>
+          <t>690984</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jorge Mateo</t>
+          <t>Petey Halpin</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-10-18T00:08:00Z</t>
@@ -9642,7 +9822,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -9652,12 +9832,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Shawn Armstrong</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>542888</t>
+          <t>607259</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -9666,7 +9846,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>30.7</v>
+        <v>33</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9680,62 +9860,58 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>23.3</v>
+        <v>7.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>32</v>
+        <v>34.3</v>
       </c>
       <c r="R15" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S15" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T15" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8</v>
+        <v>38.3</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9755,12 +9931,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -9770,12 +9946,12 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/16, 0 HR</t>
+          <t>Contact streak: 3/8 over last 7 games</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -9785,101 +9961,109 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>35.51</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>81.45</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>98.4476</t>
+          <t>93.4449</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3271</t>
+          <t>0.3143</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1223</t>
+          <t>0.0924</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.2522</t>
+          <t>0.2902</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>70.22</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>31.46</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>29.09</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1044</t>
+          <t>0.0707</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>33.38</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>0.3695</t>
+          <t>0.4114</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>0.1577</t>
+          <t>0.1502</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>29.92</t>
-        </is>
-      </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+          <t>28.96</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -9893,24 +10077,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>690984</t>
+          <t>622761</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Petey Halpin</t>
+          <t>Jorge Mateo</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-18T00:08:00Z</t>
@@ -9918,7 +10102,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -9928,12 +10112,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -9942,7 +10126,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>30.5</v>
+        <v>32.5</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -9956,26 +10140,26 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>7.1</v>
+        <v>23.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>34.3</v>
+        <v>32</v>
       </c>
       <c r="R16" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S16" t="n">
         <v>47.9</v>
       </c>
       <c r="T16" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U16" t="n">
-        <v>38.3</v>
+        <v>0.8</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -10031,12 +10215,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -10046,12 +10230,12 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Contact streak: 3/8 over last 7 games</t>
+          <t>Last 7 games: 2/16, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -10061,101 +10245,109 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>6.76</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>35.51</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>81.45</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>93.4449</t>
+          <t>98.4476</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3143</t>
+          <t>0.3271</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.0924</t>
+          <t>0.1223</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.2902</t>
+          <t>0.2522</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>70.22</t>
+          <t>73.23</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>31.46</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>29.09</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.0707</t>
+          <t>0.1044</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>28.96</t>
-        </is>
-      </c>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+          <t>29.92</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -10194,7 +10386,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -10218,7 +10410,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>29.9</v>
+        <v>31.7</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10242,7 +10434,7 @@
         <v>32</v>
       </c>
       <c r="R17" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S17" t="n">
         <v>71.7</v>
@@ -10430,8 +10622,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -10470,7 +10670,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -10494,7 +10694,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>29.8</v>
+        <v>31.6</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10518,7 +10718,7 @@
         <v>32</v>
       </c>
       <c r="R18" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S18" t="n">
         <v>59.8</v>
@@ -10706,8 +10906,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -10746,7 +10954,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -10770,7 +10978,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>27.3</v>
+        <v>29.1</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10794,7 +11002,7 @@
         <v>31.5</v>
       </c>
       <c r="R19" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S19" t="n">
         <v>40.2</v>
@@ -10982,8 +11190,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>Progressive Field</t>
